--- a/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2632_completo.xlsx
+++ b/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2632_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra4dc402f5a2b4ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd9697ce801ef4e44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Ica / Prov: Chincha / Dist.: Alto Laran</x:t>
+          <x:t>Dpto: Ica / Prov: Chincha / Dist.: Alto Larán</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,156 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0050</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2632_completo.xlsx
+++ b/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2632_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd9697ce801ef4e44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb3d233b8bfd34505"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,651 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3330</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6270</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8760</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
